--- a/wrapper/emissions_estimates.xlsx
+++ b/wrapper/emissions_estimates.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexn\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexn\Documents\GitHub\shipp\wrapper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9973B09C-1F36-41A3-8CCB-9CAC52187BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD7C6A4-9823-40A0-AAF1-E66505643925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pv" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="135">
   <si>
     <t>technology</t>
   </si>
@@ -305,9 +305,6 @@
     <t>300 kW inverter</t>
   </si>
   <si>
-    <t>seems abnormally low, 780 kgco2e per 300kW unit</t>
-  </si>
-  <si>
     <t>transformer</t>
   </si>
   <si>
@@ -429,6 +426,12 @@
   </si>
   <si>
     <t>interpolated from 80 and 100m hub height, parametric model partially based on Vestas (2022)</t>
+  </si>
+  <si>
+    <t>780 kgco2e per 300kW unit</t>
+  </si>
+  <si>
+    <t>Note results are per kWp (DC) and need to be multiplied by ILR to fit to per kW_AC units</t>
   </si>
 </sst>
 </file>
@@ -763,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26405951-BED7-478D-93AC-D6270CCEB9A6}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
@@ -780,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -809,7 +812,7 @@
         <v>2025</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>79</v>
@@ -851,7 +854,7 @@
       <c r="D4" t="s">
         <v>84</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>86</v>
       </c>
       <c r="F4" t="s">
@@ -941,16 +944,16 @@
         <v>2024</v>
       </c>
       <c r="D8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" t="s">
         <v>106</v>
       </c>
-      <c r="E8" t="s">
-        <v>107</v>
-      </c>
       <c r="F8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8" t="s">
         <v>111</v>
-      </c>
-      <c r="G8" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -973,7 +976,7 @@
         <v>91</v>
       </c>
       <c r="G9" t="s">
-        <v>92</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -987,16 +990,16 @@
         <v>2021</v>
       </c>
       <c r="D10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" t="s">
         <v>100</v>
       </c>
-      <c r="E10" t="s">
-        <v>101</v>
-      </c>
       <c r="F10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1010,16 +1013,16 @@
         <v>2021</v>
       </c>
       <c r="D11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" t="s">
         <v>100</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" t="s">
         <v>101</v>
-      </c>
-      <c r="F11" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1033,16 +1036,16 @@
         <v>2024</v>
       </c>
       <c r="D12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" t="s">
         <v>106</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>107</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>108</v>
-      </c>
-      <c r="G12" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1056,21 +1059,21 @@
         <v>2016</v>
       </c>
       <c r="D13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" t="s">
         <v>116</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>117</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>118</v>
-      </c>
-      <c r="G13" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -1085,15 +1088,15 @@
         <v>86</v>
       </c>
       <c r="F14" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" t="s">
         <v>94</v>
-      </c>
-      <c r="G14" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B15">
         <v>122.6</v>
@@ -1108,15 +1111,15 @@
         <v>86</v>
       </c>
       <c r="F15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B16">
         <v>1054.2339999999999</v>
@@ -1125,21 +1128,21 @@
         <v>2024</v>
       </c>
       <c r="D16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" t="s">
         <v>106</v>
-      </c>
-      <c r="E16" t="s">
-        <v>107</v>
       </c>
       <c r="F16" t="s">
         <v>36</v>
       </c>
       <c r="G16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B17">
         <v>6.25</v>
@@ -1154,10 +1157,15 @@
         <v>86</v>
       </c>
       <c r="F17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1165,6 +1173,7 @@
     <hyperlink ref="E3" r:id="rId1" xr:uid="{5297FE30-5A8A-4615-B232-04BCEB873A6C}"/>
     <hyperlink ref="E2" r:id="rId2" xr:uid="{A473B69B-9ABC-48BA-A1F0-9FEFA450962B}"/>
     <hyperlink ref="E9" r:id="rId3" xr:uid="{6DCFF261-E78E-4D22-8019-9F7488127F89}"/>
+    <hyperlink ref="E4" r:id="rId4" xr:uid="{ACF34708-6519-4274-99C8-6A2515615AEE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1208,7 +1217,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B2">
         <v>438.4</v>
@@ -1217,21 +1226,21 @@
         <v>2022</v>
       </c>
       <c r="D2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F2" t="s">
         <v>123</v>
       </c>
-      <c r="E2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>124</v>
-      </c>
-      <c r="G2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B3">
         <v>480.5</v>
@@ -1240,21 +1249,21 @@
         <v>2025</v>
       </c>
       <c r="D3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>127</v>
       </c>
-      <c r="F3" t="s">
-        <v>128</v>
-      </c>
       <c r="G3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B4">
         <v>309.3</v>
@@ -1263,19 +1272,22 @@
         <v>2019</v>
       </c>
       <c r="D4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" t="s">
         <v>129</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>130</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>131</v>
       </c>
-      <c r="G4" t="s">
-        <v>132</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{BBD4F419-1680-418A-A7E1-BF41BDA74469}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1328,7 +1340,7 @@
       <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
@@ -1704,7 +1716,7 @@
       <c r="D19" t="s">
         <v>38</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F19" t="s">
@@ -1788,6 +1800,8 @@
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" xr:uid="{100EF264-67B4-48F0-81B5-977E30670DD2}"/>
     <hyperlink ref="E18" r:id="rId2" xr:uid="{2F88AA36-F07D-41E2-8B16-3FE86A9B12E6}"/>
+    <hyperlink ref="E2" r:id="rId3" xr:uid="{1120A09A-DA50-405F-A6A0-F9E164FB0D6E}"/>
+    <hyperlink ref="E19" r:id="rId4" xr:uid="{6CC701F4-9BBA-4083-BC14-C270390ED74C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
